--- a/csvpp_manual/CSVPP_Converting_LibreCalc_CSV.xlsx
+++ b/csvpp_manual/CSVPP_Converting_LibreCalc_CSV.xlsx
@@ -5,16 +5,16 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="初めにLibreCalcの設定" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Excel→CSV変換(csvmake)" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Excel→CSV変換(csvmake3)" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="CSV→Excel変換(csvmake2)" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="CSV→Excel変換(csvmake4)" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="work" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Excel→CSV変換(csvmake_ooo)" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Excel→CSV変換(csvmake3_ooo)" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="CSV→Excel変換(csvmake2_ooo)" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="CSV→Excel変換(csvmake4_ooo)" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="work" sheetId="7" state="hidden" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,21 +26,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="104">
   <si>
     <t xml:space="preserve">目次</t>
   </si>
   <si>
-    <t xml:space="preserve">Excel→CSV変換(csvmake)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excel→CSV変換(csvmake3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSV→Excel変換(csvmake2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSV→Excel変換(csvmake4)</t>
+    <t xml:space="preserve">Excel→CSV変換(csvmake_ooo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excel→CSV変換(csvmake3_ooo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSV→Excel変換(csvmake2_ooo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSV→Excel変換(csvmake4_ooo)</t>
   </si>
   <si>
     <t xml:space="preserve">初めにLibreCalcの設定</t>
@@ -88,13 +88,13 @@
     <t xml:space="preserve">1. 概要</t>
   </si>
   <si>
-    <t xml:space="preserve">Excel ファイルの全シートを CSV 形式のファイルとして出力するソフトです。</t>
+    <t xml:space="preserve">LibreCalc(LibreOffice)を使用してExcel ファイルの全シートを CSV 形式のファイルとして出力するソフトです。</t>
   </si>
   <si>
     <t xml:space="preserve">CSV 形式へ変換するため、Excel 側の設定に依存しない安定した値で出力できます。</t>
   </si>
   <si>
-    <t xml:space="preserve">(Microsoft Excelが必要です)</t>
+    <t xml:space="preserve">(LibreOfficeが必要です)</t>
   </si>
   <si>
     <t xml:space="preserve">2. 使用方法</t>
@@ -103,7 +103,7 @@
     <t xml:space="preserve">%exec</t>
   </si>
   <si>
-    <t xml:space="preserve">csvmake  </t>
+    <t xml:space="preserve">csvmake_ooo  </t>
   </si>
   <si>
     <t xml:space="preserve">Excelファイル名</t>
@@ -142,91 +142,91 @@
     <t xml:space="preserve">-tmp：CSV をテンポラリディレクトリに出力し、最後にコピーする</t>
   </si>
   <si>
+    <t xml:space="preserve">-proc：csvmake_ooo 実行後、Excel のプロセスが残っていればチェックし、残っていれば削除する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">●実行例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">csvmake_ooo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aaa.xls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c:\csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">csvtab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aaa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bbb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sheet*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sheet_x*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. フィルタプログラムについて</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フィルタプログラムは、CSV ファイル変換時に実行される任意のバッチです。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以下の情報が引数として渡されます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第1引数：変換後 CSV ファイル名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第2引数：変換元 Excel ファイル名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第3引数：シーケンス番号（0 から開始）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第4引数：出力ディレクトリ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第5引数：シート名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excel→CSV変換 (csvmake3_ooo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LibreCalc(LibreOffice)を使用して指定したディレクトリ内のすべての Excel ファイルの全シートを CSV 形式で出力するツールです。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">csvmake3_ooo  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excelファイルのあるディレクトリ</t>
+  </si>
+  <si>
     <t xml:space="preserve">-proc：csvmake 実行後、Excel のプロセスが残っていればチェックし、残っていれば削除する</t>
   </si>
   <si>
-    <t xml:space="preserve">●実行例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">csvmake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aaa.xls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c:\csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">csvtab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aaa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bbb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sheet*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sheet_x*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. フィルタプログラムについて</t>
-  </si>
-  <si>
-    <t xml:space="preserve">フィルタプログラムは、CSV ファイル変換時に実行される任意のバッチです。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">以下の情報が引数として渡されます。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">第1引数：変換後 CSV ファイル名</t>
-  </si>
-  <si>
-    <t xml:space="preserve">第2引数：変換元 Excel ファイル名</t>
-  </si>
-  <si>
-    <t xml:space="preserve">第3引数：シーケンス番号（0 から開始）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">第4引数：出力ディレクトリ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">第5引数：シート名</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excel→CSV変換 (csvmake3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">指定したディレクトリ内のすべての Excel ファイルの全シートを CSV 形式で出力するツールです。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（Microsoft Excelが必要です)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">csvmake3  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excelファイルのあるディレクトリ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">csvmake3</t>
+    <t xml:space="preserve">csvmake3_ooo</t>
   </si>
   <si>
     <t xml:space="preserve">c:\excel</t>
   </si>
   <si>
-    <t xml:space="preserve">CSV ファイルの内容を Excel ファイルへ追加するツールです。</t>
+    <t xml:space="preserve">LibreCalc(LibreOffice)を使用して CSV ファイルの内容を Excel ファイルへ追加するツールです。</t>
   </si>
   <si>
     <t xml:space="preserve">追加先は新規シートとなり、既存シートがある場合は内容をコピーして新しいシートへ貼り付けます。</t>
@@ -241,7 +241,7 @@
     <t xml:space="preserve">※シート名は 32 文字以上の場合、31 文字に切り詰められます。</t>
   </si>
   <si>
-    <t xml:space="preserve">csvmake2</t>
+    <t xml:space="preserve">csvmake2_ooo</t>
   </si>
   <si>
     <t xml:space="preserve">[-x フィルタプログラム名] </t>
@@ -322,13 +322,13 @@
     <t xml:space="preserve">第2引数：変換元 CSV ファイル名</t>
   </si>
   <si>
-    <t xml:space="preserve">指定した CSV ファイル群の内容を Excel ファイルへ追加するツールです。</t>
+    <t xml:space="preserve">LibreCalc(LibreOffice)を使用して 指定した CSV ファイル群の内容を Excel ファイルへ追加するツールです。</t>
   </si>
   <si>
     <t xml:space="preserve">csvmake2 の複数 CSV 対応版です。</t>
   </si>
   <si>
-    <t xml:space="preserve">csvmake4</t>
+    <t xml:space="preserve">csvmake4_ooo</t>
   </si>
   <si>
     <t xml:space="preserve">CSVファイルのあるディレクトリ</t>
@@ -473,7 +473,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -498,19 +498,23 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -554,9 +558,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2293200</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>126000</xdr:rowOff>
+      <xdr:colOff>2292840</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>77760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -569,8 +573,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="510840" y="1078920"/>
-          <a:ext cx="2009520" cy="5172120"/>
+          <a:off x="510840" y="1153080"/>
+          <a:ext cx="2009160" cy="5171760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -587,14 +591,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>578880</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>48240</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>126360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2152800</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>87480</xdr:rowOff>
+      <xdr:colOff>2152440</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>164880</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -604,7 +608,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="806040" y="5973480"/>
-          <a:ext cx="1573920" cy="239040"/>
+          <a:ext cx="1573560" cy="238680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -635,9 +639,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>85680</xdr:rowOff>
+      <xdr:colOff>865080</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>87120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -650,8 +654,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="285840" y="7391520"/>
-          <a:ext cx="7944480" cy="6648840"/>
+          <a:off x="285840" y="7886880"/>
+          <a:ext cx="7944120" cy="6648480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -673,7 +677,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>481680</xdr:colOff>
+      <xdr:colOff>481320</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>96840</xdr:rowOff>
     </xdr:to>
@@ -684,8 +688,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2520000" y="11261880"/>
-          <a:ext cx="2654280" cy="239040"/>
+          <a:off x="2520000" y="11905920"/>
+          <a:ext cx="2653920" cy="238680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1046,136 +1050,133 @@
       </c>
       <c r="F1" s="5"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0"/>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0"/>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0"/>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0"/>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0"/>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0"/>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0"/>
-    </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="0"/>
-    </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="0"/>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="0"/>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="8"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="8"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="8"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="8"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="8"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="8"/>
+    </row>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="8"/>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="8"/>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="8"/>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="0"/>
-    </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="0"/>
-    </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="0"/>
-    </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="0"/>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="0"/>
-    </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="0"/>
-    </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="8"/>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="8"/>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="8"/>
+    </row>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="8"/>
+    </row>
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="8"/>
+    </row>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="8"/>
+    </row>
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="8" t="s">
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="9" t="s">
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="0"/>
+      <c r="B81" s="8"/>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="0"/>
+      <c r="B82" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1198,8 +1199,8 @@
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="3.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="12.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="10.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="11.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="17.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="24.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="14.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="4" width="18.87"/>
@@ -1246,31 +1247,31 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="12" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1312,122 +1313,122 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="H20" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="I20" s="13" t="s">
+      <c r="I20" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J20" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="K20" s="13" t="s">
+      <c r="K20" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="H21" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I21" s="13" t="s">
+      <c r="I21" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="J21" s="13" t="s">
+      <c r="J21" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="K21" s="13" t="s">
+      <c r="K21" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="L21" s="13" t="s">
+      <c r="L21" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="M21" s="13" t="s">
+      <c r="M21" s="14" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1492,7 +1493,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="3.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="12.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="10.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="21.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="24.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="14.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="4" width="18.87"/>
@@ -1520,7 +1521,7 @@
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1529,31 +1530,31 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="12" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1582,7 +1583,7 @@
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1591,122 +1592,122 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="H19" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="I19" s="13" t="s">
+      <c r="I19" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="J19" s="13" t="s">
+      <c r="J19" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="K19" s="13" t="s">
+      <c r="K19" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="H20" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I20" s="13" t="s">
+      <c r="I20" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J20" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="K20" s="13" t="s">
+      <c r="K20" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="L20" s="13" t="s">
+      <c r="L20" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="M20" s="13" t="s">
+      <c r="M20" s="14" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1771,7 +1772,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="3.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="13.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="11.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="20.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="24.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="4" width="21.63"/>
@@ -1816,7 +1817,7 @@
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1835,37 +1836,37 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="K14" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="L14" s="12" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1920,65 +1921,65 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="G27" s="10"/>
-      <c r="H27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="G28" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="H28" s="11"/>
+      <c r="H28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="12" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2023,12 +2024,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="3.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="13.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="11.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="18.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="24.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="4" width="20.87"/>
@@ -2061,169 +2062,174 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="10" t="s">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D9" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E9" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G9" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H9" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I9" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J9" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K9" s="12" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="10" t="s">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C22" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D22" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E22" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="10" t="s">
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C23" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D23" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E23" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F23" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G22" s="10"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="10" t="s">
+      <c r="G23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C24" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E24" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F24" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G24" s="11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="4" t="s">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="4" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="4" t="s">
         <v>97</v>
       </c>
     </row>
